--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/129.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/129.xlsx
@@ -426,13 +426,13 @@
         <v>-11.83717702021826</v>
       </c>
       <c r="E2">
-        <v>-28.50140688413746</v>
+        <v>-34.00213294006962</v>
       </c>
       <c r="F2">
-        <v>-3.660824919624433</v>
+        <v>-4.637076613008721</v>
       </c>
       <c r="G2">
-        <v>-16.36879659213513</v>
+        <v>-19.32401465758526</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.56515417569633</v>
       </c>
       <c r="E3">
-        <v>-28.82763815165003</v>
+        <v>-34.26185224559454</v>
       </c>
       <c r="F3">
-        <v>-3.565362203391012</v>
+        <v>-4.469044770453049</v>
       </c>
       <c r="G3">
-        <v>-16.29514688552296</v>
+        <v>-18.88158507535321</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.17349565839859</v>
       </c>
       <c r="E4">
-        <v>-28.79974275176278</v>
+        <v>-33.96447867869584</v>
       </c>
       <c r="F4">
-        <v>-3.63860810588135</v>
+        <v>-4.574845511873407</v>
       </c>
       <c r="G4">
-        <v>-15.83328771152093</v>
+        <v>-19.02774069509373</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.68846998356709</v>
       </c>
       <c r="E5">
-        <v>-29.37847720146905</v>
+        <v>-34.88245470173872</v>
       </c>
       <c r="F5">
-        <v>-3.555713379883203</v>
+        <v>-4.544058408980961</v>
       </c>
       <c r="G5">
-        <v>-15.9964380167873</v>
+        <v>-18.88264941574409</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.10972830219297</v>
       </c>
       <c r="E6">
-        <v>-29.42416044725842</v>
+        <v>-35.00031955897336</v>
       </c>
       <c r="F6">
-        <v>-3.63138805559855</v>
+        <v>-4.579474428920251</v>
       </c>
       <c r="G6">
-        <v>-15.47777153660414</v>
+        <v>-18.82328636840665</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.460214898853874</v>
       </c>
       <c r="E7">
-        <v>-30.07585993441328</v>
+        <v>-35.28835994094224</v>
       </c>
       <c r="F7">
-        <v>-3.752766246028553</v>
+        <v>-4.572116041281183</v>
       </c>
       <c r="G7">
-        <v>-15.23289710415533</v>
+        <v>-18.47341467363431</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.763956394182019</v>
       </c>
       <c r="E8">
-        <v>-29.93429077998548</v>
+        <v>-35.24006150141344</v>
       </c>
       <c r="F8">
-        <v>-3.711716499382823</v>
+        <v>-4.487428728223378</v>
       </c>
       <c r="G8">
-        <v>-15.15745970295196</v>
+        <v>-18.05855200410777</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.038662554789489</v>
       </c>
       <c r="E9">
-        <v>-30.69614992585093</v>
+        <v>-35.70831929922857</v>
       </c>
       <c r="F9">
-        <v>-3.561399293736019</v>
+        <v>-4.619339610179977</v>
       </c>
       <c r="G9">
-        <v>-15.0841857432585</v>
+        <v>-18.0495340780588</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.305220579466048</v>
       </c>
       <c r="E10">
-        <v>-31.13701498439367</v>
+        <v>-36.31863985513834</v>
       </c>
       <c r="F10">
-        <v>-3.634914415632267</v>
+        <v>-4.55435832926737</v>
       </c>
       <c r="G10">
-        <v>-14.6519526412874</v>
+        <v>-17.82505095085913</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.596779961443604</v>
       </c>
       <c r="E11">
-        <v>-31.4605653952937</v>
+        <v>-36.55901578393949</v>
       </c>
       <c r="F11">
-        <v>-3.552153056785971</v>
+        <v>-4.601337529782338</v>
       </c>
       <c r="G11">
-        <v>-14.50321976184457</v>
+        <v>-17.68606928330222</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.931629524683734</v>
       </c>
       <c r="E12">
-        <v>-31.41885362120905</v>
+        <v>-36.85703012991026</v>
       </c>
       <c r="F12">
-        <v>-3.543720276625472</v>
+        <v>-4.474735654510281</v>
       </c>
       <c r="G12">
-        <v>-14.3928825895662</v>
+        <v>-17.55215937151146</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.326252000264337</v>
       </c>
       <c r="E13">
-        <v>-32.3349865553308</v>
+        <v>-37.30531282887757</v>
       </c>
       <c r="F13">
-        <v>-3.487937187353551</v>
+        <v>-4.501427308963287</v>
       </c>
       <c r="G13">
-        <v>-14.4922386822908</v>
+        <v>-17.31176576245006</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.807945786044379</v>
       </c>
       <c r="E14">
-        <v>-32.65752938076412</v>
+        <v>-38.10591533411564</v>
       </c>
       <c r="F14">
-        <v>-3.338739934435332</v>
+        <v>-4.473978526704123</v>
       </c>
       <c r="G14">
-        <v>-14.04877786512327</v>
+        <v>-16.97662930587302</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.382876936859887</v>
       </c>
       <c r="E15">
-        <v>-33.48611559113259</v>
+        <v>-38.39817398962266</v>
       </c>
       <c r="F15">
-        <v>-3.242998886754571</v>
+        <v>-4.376680148306098</v>
       </c>
       <c r="G15">
-        <v>-13.85404164486672</v>
+        <v>-16.63999151689392</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.049698481239465</v>
       </c>
       <c r="E16">
-        <v>-33.70724550540114</v>
+        <v>-38.90301280047176</v>
       </c>
       <c r="F16">
-        <v>-3.244991938725706</v>
+        <v>-4.224224098025267</v>
       </c>
       <c r="G16">
-        <v>-13.44085245611029</v>
+        <v>-16.60594090074974</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.811732511352798</v>
       </c>
       <c r="E17">
-        <v>-34.8871665789437</v>
+        <v>-39.36452543625248</v>
       </c>
       <c r="F17">
-        <v>-3.084548769947081</v>
+        <v>-4.12051912613399</v>
       </c>
       <c r="G17">
-        <v>-13.18341781388548</v>
+        <v>-16.62455775358984</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.654575329274154</v>
       </c>
       <c r="E18">
-        <v>-35.60059595953411</v>
+        <v>-39.72294509701157</v>
       </c>
       <c r="F18">
-        <v>-2.875701608720673</v>
+        <v>-4.022789996686511</v>
       </c>
       <c r="G18">
-        <v>-13.16533561414998</v>
+        <v>-16.33929963138023</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.557491554221367</v>
       </c>
       <c r="E19">
-        <v>-36.19675824145889</v>
+        <v>-40.43065048645629</v>
       </c>
       <c r="F19">
-        <v>-2.852816302483531</v>
+        <v>-3.853360698322316</v>
       </c>
       <c r="G19">
-        <v>-12.99221394571933</v>
+        <v>-16.22494511208995</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.507391877575429</v>
       </c>
       <c r="E20">
-        <v>-36.23467289008811</v>
+        <v>-41.25564108846266</v>
       </c>
       <c r="F20">
-        <v>-2.66774080061526</v>
+        <v>-3.818923808653135</v>
       </c>
       <c r="G20">
-        <v>-12.80356912925504</v>
+        <v>-16.22675929104547</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.48506138717057</v>
       </c>
       <c r="E21">
-        <v>-37.36695215283297</v>
+        <v>-41.54805597632296</v>
       </c>
       <c r="F21">
-        <v>-2.597396669136928</v>
+        <v>-3.602907127555497</v>
       </c>
       <c r="G21">
-        <v>-12.90844390139361</v>
+        <v>-16.01208199973312</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.471211548587443</v>
       </c>
       <c r="E22">
-        <v>-37.37719329680132</v>
+        <v>-41.91891761941812</v>
       </c>
       <c r="F22">
-        <v>-2.385814238746476</v>
+        <v>-3.515666786162264</v>
       </c>
       <c r="G22">
-        <v>-12.60922024282659</v>
+        <v>-16.00180937692476</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.458863934244566</v>
       </c>
       <c r="E23">
-        <v>-37.81511258300207</v>
+        <v>-42.36114801287417</v>
       </c>
       <c r="F23">
-        <v>-2.191372386654751</v>
+        <v>-3.395773030118078</v>
       </c>
       <c r="G23">
-        <v>-12.69778726763871</v>
+        <v>-15.80617103300876</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.443482550303638</v>
       </c>
       <c r="E24">
-        <v>-37.96499827994495</v>
+        <v>-42.54497915097855</v>
       </c>
       <c r="F24">
-        <v>-2.284335918433925</v>
+        <v>-3.191850513101312</v>
       </c>
       <c r="G24">
-        <v>-12.78357012365231</v>
+        <v>-15.84808916062702</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.421707751693143</v>
       </c>
       <c r="E25">
-        <v>-38.53493390465431</v>
+        <v>-42.46677240486608</v>
       </c>
       <c r="F25">
-        <v>-1.958100812556799</v>
+        <v>-3.152033377150949</v>
       </c>
       <c r="G25">
-        <v>-12.509950224286</v>
+        <v>-16.05678595142267</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.400279317179177</v>
       </c>
       <c r="E26">
-        <v>-38.64853520361073</v>
+        <v>-42.57260510666234</v>
       </c>
       <c r="F26">
-        <v>-1.979372459093287</v>
+        <v>-3.21705441969889</v>
       </c>
       <c r="G26">
-        <v>-12.83999837236918</v>
+        <v>-16.11763377843447</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.387625431719841</v>
       </c>
       <c r="E27">
-        <v>-38.60358330637359</v>
+        <v>-42.42553159207823</v>
       </c>
       <c r="F27">
-        <v>-1.877246355471747</v>
+        <v>-3.002499807067193</v>
       </c>
       <c r="G27">
-        <v>-12.7467138201636</v>
+        <v>-16.15133182147872</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.388000512650327</v>
       </c>
       <c r="E28">
-        <v>-38.58076206161194</v>
+        <v>-42.56297077821102</v>
       </c>
       <c r="F28">
-        <v>-1.900866423595172</v>
+        <v>-3.065148405373517</v>
       </c>
       <c r="G28">
-        <v>-12.779498152639</v>
+        <v>-16.37201940821761</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.412288607678129</v>
       </c>
       <c r="E29">
-        <v>-38.48022088169363</v>
+        <v>-42.82021527269075</v>
       </c>
       <c r="F29">
-        <v>-1.75533138296473</v>
+        <v>-3.110229816168672</v>
       </c>
       <c r="G29">
-        <v>-12.89106684785798</v>
+        <v>-15.98008557709607</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.471431720749141</v>
       </c>
       <c r="E30">
-        <v>-38.28051517795537</v>
+        <v>-43.00324713513277</v>
       </c>
       <c r="F30">
-        <v>-1.655889189728261</v>
+        <v>-2.81668705821043</v>
       </c>
       <c r="G30">
-        <v>-12.89926044806768</v>
+        <v>-16.38829736063421</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.566675265571213</v>
       </c>
       <c r="E31">
-        <v>-38.0588418468059</v>
+        <v>-42.24992642700879</v>
       </c>
       <c r="F31">
-        <v>-1.813431415862282</v>
+        <v>-2.933205217088209</v>
       </c>
       <c r="G31">
-        <v>-12.76997040257698</v>
+        <v>-16.63859777722189</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.702733837629586</v>
       </c>
       <c r="E32">
-        <v>-37.38734160705251</v>
+        <v>-42.01280194254515</v>
       </c>
       <c r="F32">
-        <v>-1.921097640673745</v>
+        <v>-3.154609599773655</v>
       </c>
       <c r="G32">
-        <v>-13.20521444571604</v>
+        <v>-16.33346976068557</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.883077930216209</v>
       </c>
       <c r="E33">
-        <v>-37.74166299883466</v>
+        <v>-41.80935798351355</v>
       </c>
       <c r="F33">
-        <v>-1.926909466371786</v>
+        <v>-3.107597264562575</v>
       </c>
       <c r="G33">
-        <v>-12.97244998884988</v>
+        <v>-16.70494442037442</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.098418949169755</v>
       </c>
       <c r="E34">
-        <v>-37.32231951301338</v>
+        <v>-41.52716159725156</v>
       </c>
       <c r="F34">
-        <v>-1.928975414674368</v>
+        <v>-2.898058416554829</v>
       </c>
       <c r="G34">
-        <v>-13.62798766380867</v>
+        <v>-16.51245440526626</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.344065939221567</v>
       </c>
       <c r="E35">
-        <v>-36.30940629663669</v>
+        <v>-41.01066423006971</v>
       </c>
       <c r="F35">
-        <v>-1.967213682354996</v>
+        <v>-3.120158627858626</v>
       </c>
       <c r="G35">
-        <v>-13.61678643297654</v>
+        <v>-16.72310772847563</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.616011009729872</v>
       </c>
       <c r="E36">
-        <v>-36.36947197587444</v>
+        <v>-40.94263749352649</v>
       </c>
       <c r="F36">
-        <v>-1.851256328208913</v>
+        <v>-2.982223029781467</v>
       </c>
       <c r="G36">
-        <v>-13.79265585420479</v>
+        <v>-16.78364933002505</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.900018836737879</v>
       </c>
       <c r="E37">
-        <v>-36.28964630030423</v>
+        <v>-40.43258414485756</v>
       </c>
       <c r="F37">
-        <v>-1.847372941824589</v>
+        <v>-2.937457226966778</v>
       </c>
       <c r="G37">
-        <v>-13.35863174709695</v>
+        <v>-16.63768572192582</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.185469289038104</v>
       </c>
       <c r="E38">
-        <v>-35.38089930728898</v>
+        <v>-39.97382934974752</v>
       </c>
       <c r="F38">
-        <v>-1.832550963886297</v>
+        <v>-3.028018493277834</v>
       </c>
       <c r="G38">
-        <v>-13.27369970128694</v>
+        <v>-16.96250155278418</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.466904406390866</v>
       </c>
       <c r="E39">
-        <v>-35.71975596033494</v>
+        <v>-39.51451981657154</v>
       </c>
       <c r="F39">
-        <v>-1.804952247127226</v>
+        <v>-3.107339642300304</v>
       </c>
       <c r="G39">
-        <v>-13.52012015850259</v>
+        <v>-16.89870402969688</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.733262995161453</v>
       </c>
       <c r="E40">
-        <v>-34.94631297795788</v>
+        <v>-39.10318720126982</v>
       </c>
       <c r="F40">
-        <v>-1.817574909611085</v>
+        <v>-3.171171977625229</v>
       </c>
       <c r="G40">
-        <v>-13.81105752158483</v>
+        <v>-16.6166389286599</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.976800724717955</v>
       </c>
       <c r="E41">
-        <v>-34.1406249964092</v>
+        <v>-38.41404629101955</v>
       </c>
       <c r="F41">
-        <v>-1.847336493658866</v>
+        <v>-2.943220178988055</v>
       </c>
       <c r="G41">
-        <v>-13.64095507068599</v>
+        <v>-16.94843504478781</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.198658303432379</v>
       </c>
       <c r="E42">
-        <v>-33.78613831532577</v>
+        <v>-38.61685626369007</v>
       </c>
       <c r="F42">
-        <v>-1.78218705416349</v>
+        <v>-2.96006420175658</v>
       </c>
       <c r="G42">
-        <v>-13.69662520447438</v>
+        <v>-16.94698171529608</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.396818853382124</v>
       </c>
       <c r="E43">
-        <v>-33.32165273635902</v>
+        <v>-37.97479336922354</v>
       </c>
       <c r="F43">
-        <v>-1.648387494528508</v>
+        <v>-2.840486882060263</v>
       </c>
       <c r="G43">
-        <v>-13.75698472601914</v>
+        <v>-16.99196209753815</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.568716786891625</v>
       </c>
       <c r="E44">
-        <v>-33.02648000782806</v>
+        <v>-37.25797216160139</v>
       </c>
       <c r="F44">
-        <v>-1.713386999523977</v>
+        <v>-2.706464491593928</v>
       </c>
       <c r="G44">
-        <v>-13.703590592289</v>
+        <v>-16.76406414261472</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.72043583150063</v>
       </c>
       <c r="E45">
-        <v>-32.10836133785394</v>
+        <v>-36.8405193136783</v>
       </c>
       <c r="F45">
-        <v>-1.599797947782498</v>
+        <v>-2.847056663931866</v>
       </c>
       <c r="G45">
-        <v>-13.64344625620429</v>
+        <v>-16.87697029823157</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.854886749660974</v>
       </c>
       <c r="E46">
-        <v>-31.66192172780776</v>
+        <v>-36.39067429117835</v>
       </c>
       <c r="F46">
-        <v>-1.613968828942189</v>
+        <v>-2.754297738901183</v>
       </c>
       <c r="G46">
-        <v>-13.67816229200186</v>
+        <v>-17.07576524731926</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.969021743772529</v>
       </c>
       <c r="E47">
-        <v>-31.41222167102481</v>
+        <v>-36.02412149110148</v>
       </c>
       <c r="F47">
-        <v>-1.581500140222059</v>
+        <v>-2.735233691493155</v>
       </c>
       <c r="G47">
-        <v>-13.30696075232</v>
+        <v>-16.89733677438916</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.067720690068734</v>
       </c>
       <c r="E48">
-        <v>-31.07701270379204</v>
+        <v>-35.58583992698011</v>
       </c>
       <c r="F48">
-        <v>-1.559729816509086</v>
+        <v>-2.730702521799842</v>
       </c>
       <c r="G48">
-        <v>-13.56688823533588</v>
+        <v>-16.95287448635598</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.154678077204561</v>
       </c>
       <c r="E49">
-        <v>-30.71040556202707</v>
+        <v>-35.57185147077042</v>
       </c>
       <c r="F49">
-        <v>-1.457990560464653</v>
+        <v>-2.542500761353405</v>
       </c>
       <c r="G49">
-        <v>-13.44588117478444</v>
+        <v>-17.06726707691995</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.224238329901413</v>
       </c>
       <c r="E50">
-        <v>-30.0643032687457</v>
+        <v>-34.91696393791417</v>
       </c>
       <c r="F50">
-        <v>-1.568976053459134</v>
+        <v>-2.61726671802788</v>
       </c>
       <c r="G50">
-        <v>-13.57074833143467</v>
+        <v>-17.07627672660508</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.278551456960163</v>
       </c>
       <c r="E51">
-        <v>-29.43846136817465</v>
+        <v>-34.24656411734464</v>
       </c>
       <c r="F51">
-        <v>-1.331796241954774</v>
+        <v>-2.593410565194657</v>
       </c>
       <c r="G51">
-        <v>-13.70211408897849</v>
+        <v>-16.93289203348094</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.322729905095537</v>
       </c>
       <c r="E52">
-        <v>-29.0109960642206</v>
+        <v>-33.81698401602902</v>
       </c>
       <c r="F52">
-        <v>-1.49113602535287</v>
+        <v>-2.612941811817864</v>
       </c>
       <c r="G52">
-        <v>-13.59166601342455</v>
+        <v>-17.15363755476677</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.350099870149462</v>
       </c>
       <c r="E53">
-        <v>-28.60754072945523</v>
+        <v>-33.73191889603194</v>
       </c>
       <c r="F53">
-        <v>-1.407460977261286</v>
+        <v>-2.573138758113348</v>
       </c>
       <c r="G53">
-        <v>-13.86524453097162</v>
+        <v>-17.42549127808787</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.36158033572847</v>
       </c>
       <c r="E54">
-        <v>-28.2104886569367</v>
+        <v>-32.99969181983568</v>
       </c>
       <c r="F54">
-        <v>-1.4488611233184</v>
+        <v>-2.573035212187998</v>
       </c>
       <c r="G54">
-        <v>-13.51701155624122</v>
+        <v>-17.31950912846641</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.364494224437557</v>
       </c>
       <c r="E55">
-        <v>-27.91195806492905</v>
+        <v>-33.11103341026227</v>
       </c>
       <c r="F55">
-        <v>-1.487190511413336</v>
+        <v>-2.585990878367782</v>
       </c>
       <c r="G55">
-        <v>-13.83701881970379</v>
+        <v>-17.42640829920225</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.354137530333284</v>
       </c>
       <c r="E56">
-        <v>-27.49694153602209</v>
+        <v>-32.52873957998598</v>
       </c>
       <c r="F56">
-        <v>-1.302131576893121</v>
+        <v>-2.463558176234015</v>
       </c>
       <c r="G56">
-        <v>-13.74163703689908</v>
+        <v>-17.31806407533852</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.331322023594529</v>
       </c>
       <c r="E57">
-        <v>-26.84022676390374</v>
+        <v>-32.47607795575078</v>
       </c>
       <c r="F57">
-        <v>-1.294211556154955</v>
+        <v>-2.53329097256908</v>
       </c>
       <c r="G57">
-        <v>-13.92495353031791</v>
+        <v>-17.21959355354567</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.305543010327595</v>
       </c>
       <c r="E58">
-        <v>-26.98046907544729</v>
+        <v>-31.81694724274934</v>
       </c>
       <c r="F58">
-        <v>-1.472893718408419</v>
+        <v>-2.698412760438717</v>
       </c>
       <c r="G58">
-        <v>-13.73260752394072</v>
+        <v>-17.3412064439308</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.276431059446092</v>
       </c>
       <c r="E59">
-        <v>-26.36681556266787</v>
+        <v>-31.98047043916632</v>
       </c>
       <c r="F59">
-        <v>-1.495770740971533</v>
+        <v>-2.58088896353394</v>
       </c>
       <c r="G59">
-        <v>-13.82088653129092</v>
+        <v>-16.9850960260897</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.244748528325144</v>
       </c>
       <c r="E60">
-        <v>-26.35048588539621</v>
+        <v>-31.53677961284279</v>
       </c>
       <c r="F60">
-        <v>-1.598016957866479</v>
+        <v>-2.643834117370466</v>
       </c>
       <c r="G60">
-        <v>-13.76359423018829</v>
+        <v>-17.53172999498862</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.220848905136022</v>
       </c>
       <c r="E61">
-        <v>-26.17304215987966</v>
+        <v>-31.67960994728172</v>
       </c>
       <c r="F61">
-        <v>-1.440060548031058</v>
+        <v>-2.646083963236469</v>
       </c>
       <c r="G61">
-        <v>-13.72324695642843</v>
+        <v>-17.36294514121442</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.207365598232788</v>
       </c>
       <c r="E62">
-        <v>-25.91399080427088</v>
+        <v>-31.43455836906765</v>
       </c>
       <c r="F62">
-        <v>-1.601486160549403</v>
+        <v>-2.58969782249531</v>
       </c>
       <c r="G62">
-        <v>-13.88040682954148</v>
+        <v>-17.55327833590374</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.203302011658874</v>
       </c>
       <c r="E63">
-        <v>-25.8778762240597</v>
+        <v>-31.29835998481295</v>
       </c>
       <c r="F63">
-        <v>-1.645684531693174</v>
+        <v>-2.812493034050056</v>
       </c>
       <c r="G63">
-        <v>-14.00107455917514</v>
+        <v>-17.2591578832855</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.216505509554923</v>
       </c>
       <c r="E64">
-        <v>-26.02108015760427</v>
+        <v>-31.25362771856519</v>
       </c>
       <c r="F64">
-        <v>-1.645069054712893</v>
+        <v>-2.645021167858677</v>
       </c>
       <c r="G64">
-        <v>-13.99544828703115</v>
+        <v>-17.50605505905881</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.248774113558973</v>
       </c>
       <c r="E65">
-        <v>-25.43368726559533</v>
+        <v>-31.01721873299476</v>
       </c>
       <c r="F65">
-        <v>-1.846443513598648</v>
+        <v>-2.866097517052615</v>
       </c>
       <c r="G65">
-        <v>-13.68791184861502</v>
+        <v>-17.59512694206567</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.293237409004706</v>
       </c>
       <c r="E66">
-        <v>-25.38566279874399</v>
+        <v>-31.15343975961949</v>
       </c>
       <c r="F66">
-        <v>-1.626057194451242</v>
+        <v>-2.879464881831591</v>
       </c>
       <c r="G66">
-        <v>-13.90146686498955</v>
+        <v>-17.36381746996402</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.349576969001509</v>
       </c>
       <c r="E67">
-        <v>-25.35309401368083</v>
+        <v>-30.59973418575362</v>
       </c>
       <c r="F67">
-        <v>-1.920045614072189</v>
+        <v>-2.959751078878322</v>
       </c>
       <c r="G67">
-        <v>-13.89544167210808</v>
+        <v>-17.29726888353359</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.413679163333803</v>
       </c>
       <c r="E68">
-        <v>-25.44907049179939</v>
+        <v>-30.93590545371303</v>
       </c>
       <c r="F68">
-        <v>-1.807880525896122</v>
+        <v>-3.078335186058682</v>
       </c>
       <c r="G68">
-        <v>-13.82560736922992</v>
+        <v>-17.04402704723427</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.470044195274522</v>
       </c>
       <c r="E69">
-        <v>-24.95044474728882</v>
+        <v>-30.85225095336933</v>
       </c>
       <c r="F69">
-        <v>-2.045708949076874</v>
+        <v>-3.052205164704775</v>
       </c>
       <c r="G69">
-        <v>-13.65438926448436</v>
+        <v>-17.2716303636047</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.509865647519459</v>
       </c>
       <c r="E70">
-        <v>-25.0234663906625</v>
+        <v>-30.87983388855005</v>
       </c>
       <c r="F70">
-        <v>-2.014004843469529</v>
+        <v>-3.228618428641971</v>
       </c>
       <c r="G70">
-        <v>-13.75622826636342</v>
+        <v>-17.34166164394245</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.527177094533092</v>
       </c>
       <c r="E71">
-        <v>-24.80050244442084</v>
+        <v>-30.7138426737989</v>
       </c>
       <c r="F71">
-        <v>-2.282620369542728</v>
+        <v>-3.249795641294541</v>
       </c>
       <c r="G71">
-        <v>-13.99033018362744</v>
+        <v>-17.3062901201281</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.506643570872482</v>
       </c>
       <c r="E72">
-        <v>-25.59418544137519</v>
+        <v>-31.06476771007529</v>
       </c>
       <c r="F72">
-        <v>-2.446898879396314</v>
+        <v>-3.315447899803416</v>
       </c>
       <c r="G72">
-        <v>-13.38575173615466</v>
+        <v>-16.79668791363147</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.439978441878187</v>
       </c>
       <c r="E73">
-        <v>-25.0421237035741</v>
+        <v>-30.5199605876345</v>
       </c>
       <c r="F73">
-        <v>-2.299760119474052</v>
+        <v>-3.490418147724935</v>
       </c>
       <c r="G73">
-        <v>-13.64716896466321</v>
+        <v>-17.13175484875219</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.328813593019285</v>
       </c>
       <c r="E74">
-        <v>-25.18588463942161</v>
+        <v>-30.89905952494962</v>
       </c>
       <c r="F74">
-        <v>-2.48268352282985</v>
+        <v>-3.488755614347517</v>
       </c>
       <c r="G74">
-        <v>-13.51443264126613</v>
+        <v>-16.77222298209626</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.16663676959289</v>
       </c>
       <c r="E75">
-        <v>-25.35518616867237</v>
+        <v>-31.14579116702053</v>
       </c>
       <c r="F75">
-        <v>-2.60207528822794</v>
+        <v>-3.438517616469935</v>
       </c>
       <c r="G75">
-        <v>-13.58068658914356</v>
+        <v>-16.99679052820718</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.951709423327317</v>
       </c>
       <c r="E76">
-        <v>-25.41707229446119</v>
+        <v>-30.87724360141766</v>
       </c>
       <c r="F76">
-        <v>-2.807367924928936</v>
+        <v>-3.644956713656406</v>
       </c>
       <c r="G76">
-        <v>-13.1682621364067</v>
+        <v>-16.89616153072272</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.692532570132906</v>
       </c>
       <c r="E77">
-        <v>-25.68156234735319</v>
+        <v>-31.16922375577322</v>
       </c>
       <c r="F77">
-        <v>-2.895080435741764</v>
+        <v>-3.73722193171502</v>
       </c>
       <c r="G77">
-        <v>-13.3812791891311</v>
+        <v>-16.80759781645614</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.391043778549871</v>
       </c>
       <c r="E78">
-        <v>-26.21947260388031</v>
+        <v>-31.48940045353754</v>
       </c>
       <c r="F78">
-        <v>-2.82560526166897</v>
+        <v>-3.778106833247592</v>
       </c>
       <c r="G78">
-        <v>-12.85191302576502</v>
+        <v>-16.71173103872993</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.049577997308992</v>
       </c>
       <c r="E79">
-        <v>-25.64434734795815</v>
+        <v>-31.53605279276456</v>
       </c>
       <c r="F79">
-        <v>-2.773157179560719</v>
+        <v>-3.964833271349643</v>
       </c>
       <c r="G79">
-        <v>-13.29581083494374</v>
+        <v>-16.56181132871126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.680233719393837</v>
       </c>
       <c r="E80">
-        <v>-26.60813341406262</v>
+        <v>-31.84654987733748</v>
       </c>
       <c r="F80">
-        <v>-3.013060663085484</v>
+        <v>-3.925732673202701</v>
       </c>
       <c r="G80">
-        <v>-12.58819496810668</v>
+        <v>-16.60481697053916</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.290723820611833</v>
       </c>
       <c r="E81">
-        <v>-26.51327999749796</v>
+        <v>-32.20946631278619</v>
       </c>
       <c r="F81">
-        <v>-3.067955742501604</v>
+        <v>-3.980800053038604</v>
       </c>
       <c r="G81">
-        <v>-12.65834211753829</v>
+        <v>-16.25350849900278</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.88675324264763</v>
       </c>
       <c r="E82">
-        <v>-27.08364129876404</v>
+        <v>-32.38230458023695</v>
       </c>
       <c r="F82">
-        <v>-2.867126349366892</v>
+        <v>-3.927093680845501</v>
       </c>
       <c r="G82">
-        <v>-12.4490858445465</v>
+        <v>-16.71305856749117</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.482859831740195</v>
       </c>
       <c r="E83">
-        <v>-27.32398552824714</v>
+        <v>-32.71334508714567</v>
       </c>
       <c r="F83">
-        <v>-2.961768981871541</v>
+        <v>-4.120076777940896</v>
       </c>
       <c r="G83">
-        <v>-12.36120079211547</v>
+        <v>-16.47491778466924</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.092105995313249</v>
       </c>
       <c r="E84">
-        <v>-28.21969504459429</v>
+        <v>-33.31116705479426</v>
       </c>
       <c r="F84">
-        <v>-3.286851828691374</v>
+        <v>-4.076727483384994</v>
       </c>
       <c r="G84">
-        <v>-12.47546096085788</v>
+        <v>-16.50029477150052</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.722600311187668</v>
       </c>
       <c r="E85">
-        <v>-29.12624572771582</v>
+        <v>-34.14459646811393</v>
       </c>
       <c r="F85">
-        <v>-3.181753542828589</v>
+        <v>-4.067288236830095</v>
       </c>
       <c r="G85">
-        <v>-12.44152786908035</v>
+        <v>-16.15327676698304</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.388170219951899</v>
       </c>
       <c r="E86">
-        <v>-29.2607866904837</v>
+        <v>-34.28441763157476</v>
       </c>
       <c r="F86">
-        <v>-3.251738991221508</v>
+        <v>-4.287446754941731</v>
       </c>
       <c r="G86">
-        <v>-12.09157341066953</v>
+        <v>-16.28023618841409</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.101736788453605</v>
       </c>
       <c r="E87">
-        <v>-30.77597107294713</v>
+        <v>-35.36816523837942</v>
       </c>
       <c r="F87">
-        <v>-3.192608469274874</v>
+        <v>-4.343671364039344</v>
       </c>
       <c r="G87">
-        <v>-12.74590273650648</v>
+        <v>-16.30801663130688</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.868324450725837</v>
       </c>
       <c r="E88">
-        <v>-31.20834524272549</v>
+        <v>-35.75838837209438</v>
       </c>
       <c r="F88">
-        <v>-3.340210286575301</v>
+        <v>-4.278677657615694</v>
       </c>
       <c r="G88">
-        <v>-12.17953129510242</v>
+        <v>-15.98857547113153</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.697359074484043</v>
       </c>
       <c r="E89">
-        <v>-32.52365636791237</v>
+        <v>-36.42726436116033</v>
       </c>
       <c r="F89">
-        <v>-3.35145703080311</v>
+        <v>-4.486423918563783</v>
       </c>
       <c r="G89">
-        <v>-12.33132973971463</v>
+        <v>-16.0760930530077</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.599090960794925</v>
       </c>
       <c r="E90">
-        <v>-33.14091228176488</v>
+        <v>-37.58390228559244</v>
       </c>
       <c r="F90">
-        <v>-3.427535949811022</v>
+        <v>-4.586512238374436</v>
       </c>
       <c r="G90">
-        <v>-12.39902708544718</v>
+        <v>-16.37375413408019</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.572487039394832</v>
       </c>
       <c r="E91">
-        <v>-34.14749242724184</v>
+        <v>-38.38889741061795</v>
       </c>
       <c r="F91">
-        <v>-3.501085863138187</v>
+        <v>-4.517806617618842</v>
       </c>
       <c r="G91">
-        <v>-12.47084606037613</v>
+        <v>-16.17387994714669</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.619484117283076</v>
       </c>
       <c r="E92">
-        <v>-35.33226576068361</v>
+        <v>-39.5052273879078</v>
       </c>
       <c r="F92">
-        <v>-3.843069890077338</v>
+        <v>-4.608783724366103</v>
       </c>
       <c r="G92">
-        <v>-12.38966817320766</v>
+        <v>-16.64480173956248</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.74312801511065</v>
       </c>
       <c r="E93">
-        <v>-36.37762096485124</v>
+        <v>-40.31774430826005</v>
       </c>
       <c r="F93">
-        <v>-3.933998951515237</v>
+        <v>-4.824683605659946</v>
       </c>
       <c r="G93">
-        <v>-12.57335710299966</v>
+        <v>-16.74740216691557</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.933250605800292</v>
       </c>
       <c r="E94">
-        <v>-38.00588587176021</v>
+        <v>-41.2406110832312</v>
       </c>
       <c r="F94">
-        <v>-3.825673346251146</v>
+        <v>-4.919308842449137</v>
       </c>
       <c r="G94">
-        <v>-13.05260491744672</v>
+        <v>-16.67906092007563</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.182235027952066</v>
       </c>
       <c r="E95">
-        <v>-39.38294726851568</v>
+        <v>-42.59617807810927</v>
       </c>
       <c r="F95">
-        <v>-3.912216202291221</v>
+        <v>-4.969121887849083</v>
       </c>
       <c r="G95">
-        <v>-13.00057307320599</v>
+        <v>-16.6125669576466</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.485294854676861</v>
       </c>
       <c r="E96">
-        <v>-40.76087813228063</v>
+        <v>-44.05627131003239</v>
       </c>
       <c r="F96">
-        <v>-4.126620052055609</v>
+        <v>-5.242286807698456</v>
       </c>
       <c r="G96">
-        <v>-13.05793820631048</v>
+        <v>-16.79313900881337</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.821911366323828</v>
       </c>
       <c r="E97">
-        <v>-42.2334020253548</v>
+        <v>-45.39077184382677</v>
       </c>
       <c r="F97">
-        <v>-4.190910474554281</v>
+        <v>-5.459777154405675</v>
       </c>
       <c r="G97">
-        <v>-13.64493765696974</v>
+        <v>-17.50355559717666</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.180945779440172</v>
       </c>
       <c r="E98">
-        <v>-43.74365942809788</v>
+        <v>-46.68706337818143</v>
       </c>
       <c r="F98">
-        <v>-4.362481931022115</v>
+        <v>-5.436175310365111</v>
       </c>
       <c r="G98">
-        <v>-13.72716664234692</v>
+        <v>-17.34637089497206</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.539875646402001</v>
       </c>
       <c r="E99">
-        <v>-45.25382399712381</v>
+        <v>-48.12762983018348</v>
       </c>
       <c r="F99">
-        <v>-4.465896974322411</v>
+        <v>-5.53598115689141</v>
       </c>
       <c r="G99">
-        <v>-13.81589091807216</v>
+        <v>-17.77992821515886</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.889201300661982</v>
       </c>
       <c r="E100">
-        <v>-47.18475172857242</v>
+        <v>-49.48906572737548</v>
       </c>
       <c r="F100">
-        <v>-4.630087677231301</v>
+        <v>-5.885722016190375</v>
       </c>
       <c r="G100">
-        <v>-14.17485171562257</v>
+        <v>-18.08521182733552</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.18881592785734</v>
       </c>
       <c r="E101">
-        <v>-48.86233964225443</v>
+        <v>-50.86064767058168</v>
       </c>
       <c r="F101">
-        <v>-4.777422760228027</v>
+        <v>-5.936548983291346</v>
       </c>
       <c r="G101">
-        <v>-14.66033494259284</v>
+        <v>-17.99952994296088</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.456978034559262</v>
       </c>
       <c r="E102">
-        <v>-50.93555429126106</v>
+        <v>-52.78489250651348</v>
       </c>
       <c r="F102">
-        <v>-4.875315906421261</v>
+        <v>-5.965581604024663</v>
       </c>
       <c r="G102">
-        <v>-14.65542871410364</v>
+        <v>-18.11350540478691</v>
       </c>
     </row>
   </sheetData>
